--- a/8上-下单词表_备份.xlsx
+++ b/8上-下单词表_备份.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lsj\python_files\wordsgame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\gitee\wordsgame\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583A1DC3-44E4-4A08-BB89-2477FCA17209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="1005" windowWidth="24975" windowHeight="13695"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="8上" sheetId="7" r:id="rId1"/>
@@ -18,15 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -7758,8 +7750,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7770,14 +7762,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
@@ -7856,46 +7840,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="nnn__2" displayName="nnn__2" ref="A1:M511" totalsRowShown="0">
-  <autoFilter ref="A1:M511">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="adj."/>
-        <filter val="adj./n."/>
-        <filter val="adj./n./v."/>
-        <filter val="adj./v."/>
-        <filter val="adj./v./n."/>
-        <filter val="adv."/>
-        <filter val="adv./conj."/>
-        <filter val="adv./pron."/>
-        <filter val="conj."/>
-        <filter val="n."/>
-        <filter val="n. [pl.]"/>
-        <filter val="n./adj."/>
-        <filter val="n./v."/>
-        <filter val="prep."/>
-        <filter val="prep./adv."/>
-        <filter val="prep./conj."/>
-        <filter val="v."/>
-        <filter val="v./n."/>
-        <filter val="v./n./adj."/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="nnn__2" displayName="nnn__2" ref="A1:M511" totalsRowShown="0">
+  <autoFilter ref="A1:M511" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="display"/>
-    <tableColumn id="2" name="use-ranking"/>
-    <tableColumn id="3" name="Grade" dataDxfId="6"/>
-    <tableColumn id="4" name="unit"/>
-    <tableColumn id="5" name="斩kill"/>
-    <tableColumn id="6" name="英文English" dataDxfId="5"/>
-    <tableColumn id="7" name="音标" dataDxfId="4"/>
-    <tableColumn id="8" name="词性" dataDxfId="3"/>
-    <tableColumn id="9" name="释义" dataDxfId="2"/>
-    <tableColumn id="10" name="例句" dataDxfId="1"/>
-    <tableColumn id="11" name="联想词" dataDxfId="0"/>
-    <tableColumn id="12" name="frequency"/>
-    <tableColumn id="13" name="id"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="display"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="use-ranking"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Grade" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="unit"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="斩kill"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="英文English" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="音标" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="词性" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="释义" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="例句" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="联想词" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="frequency"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="id"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8197,7 +8157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M511"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -9077,7 +9037,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>0</v>
       </c>
@@ -9118,7 +9078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>0</v>
       </c>
@@ -9159,7 +9119,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>0</v>
       </c>
@@ -9200,7 +9160,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>0</v>
       </c>
@@ -9241,7 +9201,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>0</v>
       </c>
@@ -9282,7 +9242,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>0</v>
       </c>
@@ -9323,7 +9283,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>0</v>
       </c>
@@ -9364,7 +9324,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>0</v>
       </c>
@@ -10348,7 +10308,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>0</v>
       </c>
@@ -10389,7 +10349,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>0</v>
       </c>
@@ -10430,7 +10390,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>0</v>
       </c>
@@ -10471,7 +10431,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>0</v>
       </c>
@@ -10512,7 +10472,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>0</v>
       </c>
@@ -10553,7 +10513,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>0</v>
       </c>
@@ -10594,7 +10554,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>0</v>
       </c>
@@ -10635,7 +10595,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>0</v>
       </c>
@@ -12193,7 +12153,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>0</v>
       </c>
@@ -12234,7 +12194,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>0</v>
       </c>
@@ -12275,7 +12235,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>0</v>
       </c>
@@ -12316,7 +12276,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>0</v>
       </c>
@@ -12357,7 +12317,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>0</v>
       </c>
@@ -12398,7 +12358,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>0</v>
       </c>
@@ -12439,7 +12399,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>0</v>
       </c>
@@ -12480,7 +12440,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>0</v>
       </c>
@@ -13587,7 +13547,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>0</v>
       </c>
@@ -13628,7 +13588,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>0</v>
       </c>
@@ -13669,7 +13629,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>0</v>
       </c>
@@ -13710,7 +13670,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>0</v>
       </c>
@@ -13751,7 +13711,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>0</v>
       </c>
@@ -13792,7 +13752,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>0</v>
       </c>
@@ -13833,7 +13793,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>0</v>
       </c>
@@ -13874,7 +13834,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>0</v>
       </c>
@@ -13915,7 +13875,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>0</v>
       </c>
@@ -13956,7 +13916,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>0</v>
       </c>
@@ -13997,7 +13957,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>0</v>
       </c>
@@ -14038,7 +13998,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>0</v>
       </c>
@@ -14079,7 +14039,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>0</v>
       </c>
@@ -14120,7 +14080,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>0</v>
       </c>
@@ -15145,7 +15105,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>0</v>
       </c>
@@ -15186,7 +15146,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>0</v>
       </c>
@@ -15227,7 +15187,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>0</v>
       </c>
@@ -15268,7 +15228,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>0</v>
       </c>
@@ -15309,7 +15269,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>0</v>
       </c>
@@ -15350,7 +15310,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>0</v>
       </c>
@@ -16457,7 +16417,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>0</v>
       </c>
@@ -16498,7 +16458,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>0</v>
       </c>
@@ -16539,7 +16499,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>0</v>
       </c>
@@ -16580,7 +16540,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>0</v>
       </c>
@@ -16621,7 +16581,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>0</v>
       </c>
@@ -16662,7 +16622,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>0</v>
       </c>
@@ -17769,7 +17729,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>0</v>
       </c>
@@ -17810,7 +17770,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>0</v>
       </c>
@@ -17851,7 +17811,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>0</v>
       </c>
@@ -17892,7 +17852,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>0</v>
       </c>
@@ -17933,7 +17893,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>0</v>
       </c>
@@ -18835,7 +18795,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>0</v>
       </c>
@@ -18876,7 +18836,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>0</v>
       </c>
@@ -18917,7 +18877,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>0</v>
       </c>
@@ -18958,7 +18918,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>0</v>
       </c>
@@ -18999,7 +18959,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="264" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>0</v>
       </c>
@@ -19040,7 +19000,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>0</v>
       </c>
@@ -19081,7 +19041,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>0</v>
       </c>
@@ -19122,7 +19082,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>0</v>
       </c>
@@ -19163,7 +19123,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="268" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>0</v>
       </c>
@@ -20106,7 +20066,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>0</v>
       </c>
@@ -20147,7 +20107,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>0</v>
       </c>
@@ -20188,7 +20148,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>0</v>
       </c>
@@ -20229,7 +20189,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>0</v>
       </c>
@@ -20270,7 +20230,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="295" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>0</v>
       </c>
@@ -20311,7 +20271,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>0</v>
       </c>
@@ -20352,7 +20312,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>0</v>
       </c>
@@ -20393,7 +20353,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>0</v>
       </c>
@@ -20434,7 +20394,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>0</v>
       </c>
@@ -20475,7 +20435,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>0</v>
       </c>
@@ -20516,7 +20476,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>0</v>
       </c>
@@ -20557,7 +20517,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>0</v>
       </c>
@@ -21459,7 +21419,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>0</v>
       </c>
@@ -21500,7 +21460,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>0</v>
       </c>
@@ -21541,7 +21501,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="326" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>0</v>
       </c>
@@ -21582,7 +21542,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="327" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>0</v>
       </c>
@@ -21623,7 +21583,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>0</v>
       </c>
@@ -22484,7 +22444,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="349" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>0</v>
       </c>
@@ -22525,7 +22485,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="350" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>0</v>
       </c>
@@ -22566,7 +22526,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="351" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>0</v>
       </c>
@@ -22607,7 +22567,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="352" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>0</v>
       </c>
@@ -22648,7 +22608,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="353" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>0</v>
       </c>
@@ -22689,7 +22649,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>0</v>
       </c>
@@ -22730,7 +22690,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="355" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>0</v>
       </c>
@@ -22771,7 +22731,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="356" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>0</v>
       </c>
@@ -22812,7 +22772,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="357" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>0</v>
       </c>
@@ -22853,7 +22813,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="358" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>0</v>
       </c>
@@ -22894,7 +22854,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="359" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>0</v>
       </c>
@@ -22935,7 +22895,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="360" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>0</v>
       </c>
@@ -22976,7 +22936,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="361" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>0</v>
       </c>
@@ -23017,7 +22977,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="362" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>0</v>
       </c>
@@ -23058,7 +23018,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="363" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>0</v>
       </c>
@@ -23099,7 +23059,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="364" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>0</v>
       </c>
@@ -23140,7 +23100,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="365" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>0</v>
       </c>
@@ -23181,7 +23141,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="366" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>0</v>
       </c>
@@ -23222,7 +23182,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="367" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>0</v>
       </c>
@@ -24042,7 +24002,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="387" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>0</v>
       </c>
@@ -24083,7 +24043,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="388" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>0</v>
       </c>
@@ -24124,7 +24084,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="389" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>0</v>
       </c>
@@ -24165,7 +24125,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="390" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>0</v>
       </c>
@@ -24206,7 +24166,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="391" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>0</v>
       </c>
@@ -24247,7 +24207,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="392" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>0</v>
       </c>
@@ -24288,7 +24248,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>0</v>
       </c>
@@ -24329,7 +24289,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="394" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>0</v>
       </c>
@@ -24370,7 +24330,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="395" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>0</v>
       </c>
@@ -25313,7 +25273,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="418" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
         <v>0</v>
       </c>
@@ -25354,7 +25314,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="419" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
         <v>0</v>
       </c>
@@ -25395,7 +25355,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="420" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
         <v>0</v>
       </c>
@@ -25436,7 +25396,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="421" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
         <v>0</v>
       </c>
@@ -25477,7 +25437,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="422" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
         <v>0</v>
       </c>
@@ -25518,7 +25478,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="423" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
         <v>0</v>
       </c>
@@ -25559,7 +25519,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="424" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
         <v>0</v>
       </c>
@@ -25600,7 +25560,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="425" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
         <v>0</v>
       </c>
@@ -25641,7 +25601,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="426" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
         <v>0</v>
       </c>
@@ -25682,7 +25642,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="427" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
         <v>0</v>
       </c>
@@ -25723,7 +25683,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="428" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
         <v>0</v>
       </c>
@@ -25764,7 +25724,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="429" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
         <v>0</v>
       </c>
@@ -25805,7 +25765,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="430" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
         <v>0</v>
       </c>
@@ -26584,7 +26544,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="449" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
         <v>0</v>
       </c>
@@ -26625,7 +26585,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="450" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
         <v>0</v>
       </c>
@@ -26666,7 +26626,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="451" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
         <v>0</v>
       </c>
@@ -26707,7 +26667,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="452" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
         <v>0</v>
       </c>
@@ -26748,7 +26708,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="453" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
         <v>0</v>
       </c>
@@ -26789,7 +26749,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="454" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
         <v>0</v>
       </c>
@@ -26830,7 +26790,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="455" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
         <v>0</v>
       </c>
@@ -26871,7 +26831,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="456" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
         <v>0</v>
       </c>
@@ -27732,7 +27692,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="477" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="1">
         <v>0</v>
       </c>
@@ -27773,7 +27733,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="478" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="1">
         <v>0</v>
       </c>
@@ -27814,7 +27774,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="479" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="1">
         <v>0</v>
       </c>
@@ -27855,7 +27815,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="480" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="1">
         <v>0</v>
       </c>
@@ -27896,7 +27856,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="481" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="1">
         <v>0</v>
       </c>
@@ -27937,7 +27897,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="482" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="1">
         <v>0</v>
       </c>
@@ -27978,7 +27938,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="483" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="1">
         <v>0</v>
       </c>
@@ -28019,7 +27979,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="484" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="1">
         <v>0</v>
       </c>
@@ -28798,7 +28758,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="503" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="1">
         <v>0</v>
       </c>
@@ -28839,7 +28799,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="504" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="1">
         <v>0</v>
       </c>
@@ -28880,7 +28840,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="505" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="1">
         <v>0</v>
       </c>
@@ -28921,7 +28881,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="506" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="1">
         <v>0</v>
       </c>
@@ -28962,7 +28922,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="507" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="1">
         <v>0</v>
       </c>
@@ -29003,7 +28963,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="508" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="1">
         <v>0</v>
       </c>
@@ -29044,7 +29004,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="509" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="1">
         <v>0</v>
       </c>
@@ -29085,7 +29045,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="510" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="1">
         <v>0</v>
       </c>
@@ -29126,7 +29086,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="511" spans="1:13" s="1" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="1">
         <v>0</v>
       </c>
